--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/869bfb2927c1b336/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAE19FB0-1A15-40A0-97C7-B6323F770E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{AAE19FB0-1A15-40A0-97C7-B6323F770E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6BCD321-5705-40E9-8051-F92762A0F1EA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{61C672DB-71A6-4B12-AF3E-2D90EAB46F19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>username</t>
   </si>
@@ -47,9 +47,6 @@
     <t>results</t>
   </si>
   <si>
-    <t>pavanoltraining@gmail.com</t>
-  </si>
-  <si>
     <t>test@123</t>
   </si>
   <si>
@@ -78,6 +75,12 @@
   </si>
   <si>
     <t>abc123@gmail.com</t>
+  </si>
+  <si>
+    <t>wisdomolalere@yahoo.com</t>
+  </si>
+  <si>
+    <t>wisdom123</t>
   </si>
 </sst>
 </file>
@@ -489,63 +492,63 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{226A8C9E-E56B-4BB0-957B-1D716B12BAD7}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{1E57B331-A1F9-4F26-B303-C8047BDEF5B1}"/>
+    <hyperlink ref="B2" r:id="rId2" display="test@123" xr:uid="{1E57B331-A1F9-4F26-B303-C8047BDEF5B1}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{630C2479-C3EB-4C42-BE68-AD006356042C}"/>
     <hyperlink ref="A4" r:id="rId4" xr:uid="{7706D1F8-4323-4D70-AF7A-9DA672C87D13}"/>
     <hyperlink ref="A5" r:id="rId5" xr:uid="{756345D9-43EF-419B-9B74-F3899B009F19}"/>
